--- a/output/静岡赤十字病院_随意契約_X線関連.xlsx
+++ b/output/静岡赤十字病院_随意契約_X線関連.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -657,7 +657,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -672,7 +672,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
